--- a/forms/trg/Formulir_TRG_odfrg.xlsx
+++ b/forms/trg/Formulir_TRG_odfrg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B36)</f>
+        <f>COUNTA(Anggota!B5:B37)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F36)</f>
+        <f>COUNTA(Anggota!F5:F37)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Sutomo Syawal, S. Pt., M. Si</t>
+          <t>Prof. Dr. Ir. Ambo Ako, M. Sc., IPU</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Department of Animal Production, Faculty of Animal Science, Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Animal production</t>
+          <t>Tatalaksana Ladang Ternak Perah (Management of Dairy Farm Operations)</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,15 +933,19 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0009-0002-1706-816X</t>
+          <t>0000-0001-8291-9560</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6694504</t>
-        </is>
-      </c>
-      <c r="L5" s="12" t="n"/>
+          <t>6015648</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>55977837800</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -958,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Agr. Ir. Renny Fatmyah Utamy, S. Pt., M. Agr., IPM</t>
+          <t>Dr. Sutomo Syawal, S. Pt., M. Si</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Manajemen Pakan Ternak Perah (Feed Management of Dairy Cows)</t>
+          <t>Animal production</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -982,19 +982,15 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7908-6710</t>
+          <t>0009-0002-1706-816X</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>https://sinta.kemdikbud.go.id/</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>55744037500</t>
-        </is>
-      </c>
+          <t>6694504</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1007,12 +1003,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Sri Gustina, S.Pt., M.Si</t>
+          <t>Dr. Agr. Ir. Renny Fatmyah Utamy, S. Pt., M. Agr., IPM</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1022,7 +1018,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Reproductive Biology</t>
+          <t>Manajemen Pakan Ternak Perah (Feed Management of Dairy Cows)</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1031,17 +1027,17 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-1466-4740</t>
+          <t>0000-0002-7908-6710</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6173147</t>
+          <t>https://sinta.kemdikbud.go.id/</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57194022996</t>
+          <t>55744037500</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1056,12 +1052,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Sutomo Syawal, S. Pt., M. Si</t>
+          <t>Dr. Sri Gustina, S.Pt., M.Si</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1071,7 +1067,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Animal production</t>
+          <t>Reproductive Biology</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1080,15 +1076,19 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0009-0002-1706-816X</t>
+          <t>0000-0003-1466-4740</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>6694504</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="n"/>
+          <t>6173147</t>
+        </is>
+      </c>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>57194022996</t>
+        </is>
+      </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Agr. Ir. Renny Fatmyah Utamy, S. Pt., M. Agr., IPM</t>
+          <t>Dr. Sutomo Syawal, S. Pt., M. Si</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Manajemen Pakan Ternak Perah (Feed Management of Dairy Cows)</t>
+          <t>Animal production</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1125,19 +1125,15 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7908-6710</t>
+          <t>0009-0002-1706-816X</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>https://sinta.kemdikbud.go.id/</t>
-        </is>
-      </c>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>55744037500</t>
-        </is>
-      </c>
+          <t>6694504</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="n"/>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1150,12 +1146,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Sri Gustina, S.Pt., M.Si</t>
+          <t>Dr. Agr. Ir. Renny Fatmyah Utamy, S. Pt., M. Agr., IPM</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1165,7 +1161,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Reproductive Biology</t>
+          <t>Manajemen Pakan Ternak Perah (Feed Management of Dairy Cows)</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1174,17 +1170,17 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-1466-4740</t>
+          <t>0000-0002-7908-6710</t>
         </is>
       </c>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>6173147</t>
+          <t>https://sinta.kemdikbud.go.id/</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>57194022996</t>
+          <t>55744037500</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1199,22 +1195,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Associate Professor Dr. Mohammad Mijanur Rahman (Malaysia)</t>
+          <t>Dr. Sri Gustina, S.Pt., M.Si</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>UNIVERSITI MALAYSIA SABAH</t>
+          <t>Department of Animal Production, Faculty of Animal Science, Hasanuddin University</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>ANIMAL NUTRITION</t>
+          <t>Reproductive Biology</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1223,13 +1219,17 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-6244-7129</t>
-        </is>
-      </c>
-      <c r="K11" s="12" t="n"/>
+          <t>0000-0003-1466-4740</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>6173147</t>
+        </is>
+      </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>55416524200</t>
+          <t>57194022996</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1244,22 +1244,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Kannika Umpuch, Ph. D (Thailand)</t>
+          <t>Associate Professor Dr. Mohammad Mijanur Rahman (Malaysia)</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Valaya Alongkorn Rajabhat University under the Royal Patronage</t>
+          <t>UNIVERSITI MALAYSIA SABAH</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Tropical Forage Crop Production, Ruminant Nutrition, Pasture Management, Silage Production</t>
+          <t>ANIMAL NUTRITION</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1268,11 +1268,15 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-7290-375X</t>
+          <t>0000-0002-6244-7129</t>
         </is>
       </c>
       <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>55416524200</t>
+        </is>
+      </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1285,22 +1289,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. Laode Alhamd, SP, M.Sc. (BRIN)</t>
+          <t>Kannika Umpuch, Ph. D (Thailand)</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>National Research and Innovation Agency-BRIN</t>
+          <t>Valaya Alongkorn Rajabhat University under the Royal Patronage</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Ecology in several aspects: cycle, dynamics, succession, etc</t>
+          <t>Tropical Forage Crop Production, Ruminant Nutrition, Pasture Management, Silage Production</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1309,19 +1313,11 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-2574-5952</t>
-        </is>
-      </c>
-      <c r="K13" s="11" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdikbud.go.id/authors?q=Laode+Alhamd</t>
-        </is>
-      </c>
-      <c r="L13" s="11" t="inlineStr">
-        <is>
-          <t>55488921400</t>
-        </is>
-      </c>
+          <t>0000-0001-7290-375X</t>
+        </is>
+      </c>
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="12" t="n"/>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1334,31 +1330,43 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>DR. NOOR SYAHEERA BINTI IBRAHIM</t>
+          <t>Dr. Laode Alhamd, SP, M.Sc. (BRIN)</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Fakulti Perubatan Veterinar, Universiti Sultan Zainal Abidin</t>
+          <t>National Research and Innovation Agency-BRIN</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Dairy Production</t>
+          <t>Ecology in several aspects: cycle, dynamics, succession, etc</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
-      <c r="K14" s="12" t="n"/>
-      <c r="L14" s="12" t="n"/>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-2574-5952</t>
+        </is>
+      </c>
+      <c r="K14" s="11" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdikbud.go.id/authors?q=Laode+Alhamd</t>
+        </is>
+      </c>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>55488921400</t>
+        </is>
+      </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1371,39 +1379,31 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Zyahrul Ramadan, S. Pt., M. Si</t>
+          <t>DR. NOOR SYAHEERA BINTI IBRAHIM</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Laboratory of Dairy Cow, Faculty of Animal Science, Hasanuddin University Makassar, South Sulawesi, Indonesia</t>
+          <t>Fakulti Perubatan Veterinar, Universiti Sultan Zainal Abidin</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Nutrition and Physiology in Dairy Science</t>
+          <t>Dairy Production</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>0009-0009-7460-103X%20</t>
-        </is>
-      </c>
+      <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
-      <c r="L15" s="11" t="inlineStr">
-        <is>
-          <t>59161668100</t>
-        </is>
-      </c>
+      <c r="L15" s="12" t="n"/>
       <c r="M15" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Rara Mufliha, S. Pt., M, Si</t>
+          <t>Zyahrul Ramadan, S. Pt., M. Si</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Dairy Feed</t>
+          <t>Nutrition and Physiology in Dairy Science</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1440,13 +1440,13 @@
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>0009-0007-1878-6629</t>
+          <t>0009-0009-7460-103X%20</t>
         </is>
       </c>
       <c r="K16" s="12" t="n"/>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>59161668000</t>
+          <t>59161668100</t>
         </is>
       </c>
       <c r="M16" s="11" t="inlineStr">
@@ -1461,22 +1461,22 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Zyahrul Ramadan (S3)</t>
+          <t>Rara Mufliha, S. Pt., M, Si</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Doctoral of Animal Science and Technology, Faculty of Animal Science, Hasanuddin University, Makassar, South Sulawesi, Indonesia</t>
+          <t>Laboratory of Dairy Cow, Faculty of Animal Science, Hasanuddin University Makassar, South Sulawesi, Indonesia</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Nutrition and Physiology in Dairy Science</t>
+          <t>Dairy Feed</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -1485,13 +1485,13 @@
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>0009-0009-7460-103X%20</t>
+          <t>0009-0007-1878-6629</t>
         </is>
       </c>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>59161668100</t>
+          <t>59161668000</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
@@ -1506,31 +1506,39 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Ikran</t>
+          <t>Zyahrul Ramadan (S3)</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Master Student of Animal Science Faculty, Hasanuddin University</t>
+          <t>Doctoral of Animal Science and Technology, Faculty of Animal Science, Hasanuddin University, Makassar, South Sulawesi, Indonesia</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Dairy Farming System</t>
+          <t>Nutrition and Physiology in Dairy Science</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
       <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>0009-0009-7460-103X%20</t>
+        </is>
+      </c>
       <c r="K18" s="12" t="n"/>
-      <c r="L18" s="12" t="n"/>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>59161668100</t>
+        </is>
+      </c>
       <c r="M18" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1543,12 +1551,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Irmayanti</t>
+          <t>Ikran</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1558,7 +1566,7 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Dairy Feed Science</t>
+          <t>Dairy Farming System</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
@@ -1580,22 +1588,22 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Hisbullah Arifin</t>
+          <t>Irmayanti</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Graduate Student of Animal Science Faculty, Hasanuddin University</t>
+          <t>Master Student of Animal Science Faculty, Hasanuddin University</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Dairy Cattle</t>
+          <t>Dairy Feed Science</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
@@ -1617,12 +1625,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Rita Nurfadilah</t>
+          <t>Hisbullah Arifin</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1654,12 +1662,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Aura Zazilia Susia</t>
+          <t>Rita Nurfadilah</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1691,12 +1699,12 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Yusuf Rifai</t>
+          <t>Aura Zazilia Susia</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -1728,12 +1736,12 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Kesya Sombo Allo</t>
+          <t>Muhammad Yusuf Rifai</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
@@ -1763,10 +1771,26 @@
       <c r="A25" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="11" t="n"/>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Kesya Sombo Allo</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Graduate Student of Animal Science Faculty, Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Dairy Cattle</t>
+        </is>
+      </c>
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="12" t="n"/>
       <c r="H25" s="12" t="n"/>
@@ -1774,7 +1798,11 @@
       <c r="J25" s="12" t="n"/>
       <c r="K25" s="12" t="n"/>
       <c r="L25" s="12" t="n"/>
-      <c r="M25" s="12" t="n"/>
+      <c r="M25" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -1963,15 +1991,32 @@
       <c r="L36" s="12" t="n"/>
       <c r="M36" s="12" t="n"/>
     </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="12" t="n"/>
+      <c r="G37" s="12" t="n"/>
+      <c r="H37" s="12" t="n"/>
+      <c r="I37" s="12" t="n"/>
+      <c r="J37" s="12" t="n"/>
+      <c r="K37" s="12" t="n"/>
+      <c r="L37" s="12" t="n"/>
+      <c r="M37" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
